--- a/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
+++ b/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId2"/>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">SIF (5 root elements)</t>
   </si>
   <si>
-    <t xml:space="preserve">SIF_detail sheet. 0/0.5/1 rubric under Criterion A (addressability), applied uniformly to all five elements. 0.30 not 0.40: the prior studies scored spatial 1.0 under a fragmentation criterion. Open for Dr. Nasim; see SIF_detail row 7.</t>
+    <t xml:space="preserve">SIF_detail sheet. 0/0.5/1 rubric under Criterion A (addressability), applied uniformly to all five elements. 0.30 not 0.40: the prior studies scored spatial 1.0 under a fragmentation criterion. See SIF_detail row 7.</t>
   </si>
   <si>
     <t xml:space="preserve">READ THE BLOCKS SEPARATELY. Coverage (recall, precision, SIF) varies with the model and the task: both models cover the answer key well, so capability is not the variable. Recoverability (TC, AC, EF) does not move at all: 0.00 unstructured, 1.00 structured, both vendors. That is the contribution, isolated. Coverage cannot explain the gap here; only the representation can.</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">NEITHER PLAN PROPOSES THE REFERENCE FIX. The human patch is one line in _cstack (cright[...] = 1 becomes = right). Both plans propose a recursion redesign instead. Refinement correctness is not what this pilot measures (Jul 21: the assurance engine is assumed to do its job); recorded so the Docker stage confirms or overturns it rather than discovering it late.</t>
   </si>
   <si>
-    <t xml:space="preserve">OPEN FOR DR. NASIM (neither blocks any conclusion; both are about what the metric measures, not what the artifacts contain)</t>
+    <t xml:space="preserve">OPEN (neither blocks any conclusion; both are about what the metric measures, not what the artifacts contain)</t>
   </si>
   <si>
     <t xml:space="preserve">Q-A. SIF spatial rubric. Prose spatial is scored 0.5 here under the addressability criterion used by TC, AC and EF: present in the document is not the same as retrievable at the node. The submitted studies scored it 1.0 under a fragmentation criterion (stated whole vs reassembled from specializations) that appears nowhere else in the metric suite. Unstructured SIF is therefore 0.30 here and 0.40 there, differing in exactly one cell. Either recompute the prior studies or report the two rubrics side by side.</t>
@@ -1193,9 +1193,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="61.99"/>
   </cols>
@@ -1343,7 +1343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
@@ -1410,14 +1410,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="74"/>
   </cols>
   <sheetData>
@@ -1645,7 +1645,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
@@ -1655,7 +1655,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2042,17 +2042,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2422,9 +2422,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="8"/>
@@ -2624,7 +2624,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="86"/>
@@ -2803,7 +2803,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
@@ -2964,12 +2964,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="45.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="45.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="50"/>
   </cols>

--- a/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
+++ b/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
@@ -16,6 +16,8 @@
     <sheet name="SIF" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="Behavior_exec" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="SIF_detail" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Plan_trajectory" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Overhead" sheetId="10" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="379">
   <si>
     <t xml:space="preserve">SPINE pilot scorecard: astropy__astropy-12907 (run 1, FINAL)</t>
   </si>
@@ -56,6 +58,12 @@
     <t xml:space="preserve">Basis</t>
   </si>
   <si>
+    <t xml:space="preserve">CLAUDE traj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI traj</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recall (/6 obligations)</t>
   </si>
   <si>
@@ -89,7 +97,7 @@
     <t xml:space="preserve">SIF (5 root elements)</t>
   </si>
   <si>
-    <t xml:space="preserve">SIF_detail sheet. 0/0.5/1 rubric under Criterion A (addressability), applied uniformly to all five elements. 0.30 not 0.40: the prior studies scored spatial 1.0 under a fragmentation criterion. See SIF_detail row 7.</t>
+    <t xml:space="preserve">SIF_detail sheet. 0/0.5/1 rubric under Criterion A (addressability), applied uniformly to all five elements. 0.30 not 0.40: the prior studies scored spatial 1.0 under a fragmentation criterion. Open for meeting; see SIF_detail row 7.</t>
   </si>
   <si>
     <t xml:space="preserve">READ THE BLOCKS SEPARATELY. Coverage (recall, precision, SIF) varies with the model and the task: both models cover the answer key well, so capability is not the variable. Recoverability (TC, AC, EF) does not move at all: 0.00 unstructured, 1.00 structured, both vendors. That is the contribution, isolated. Coverage cannot explain the gap here; only the representation can.</t>
@@ -101,7 +109,7 @@
     <t xml:space="preserve">NEITHER PLAN PROPOSES THE REFERENCE FIX. The human patch is one line in _cstack (cright[...] = 1 becomes = right). Both plans propose a recursion redesign instead. Refinement correctness is not what this pilot measures (Jul 21: the assurance engine is assumed to do its job); recorded so the Docker stage confirms or overturns it rather than discovering it late.</t>
   </si>
   <si>
-    <t xml:space="preserve">OPEN (neither blocks any conclusion; both are about what the metric measures, not what the artifacts contain)</t>
+    <t xml:space="preserve">OPEN FOR CO-AUTHOR (neither blocks any conclusion; both are about what the metric measures, not what the artifacts contain)</t>
   </si>
   <si>
     <t xml:space="preserve">Q-A. SIF spatial rubric. Prose spatial is scored 0.5 here under the addressability criterion used by TC, AC and EF: present in the document is not the same as retrievable at the node. The submitted studies scored it 1.0 under a fragmentation criterion (stated whole vs reassembled from specializations) that appears nowhere else in the metric suite. Unstructured SIF is therefore 0.30 here and 0.40 there, differing in exactly one cell. Either recompute the prior studies or report the two rubrics side by side.</t>
@@ -110,6 +118,9 @@
     <t xml:space="preserve">Q-B. Does SIF score field PRESENCE or AGREEMENT with the ground-truth value? Gemini structured carries context = 'issue-resolution' where the GT root has 'production'. Scored 1.0 here on presence: the field is populated and readable, so the lineage question can be answered, which is what SIF measures. Whether the value is the right one is a refinement-quality question, and quality is out of scope for this stage per the Jul 21 direction that the assurance engine is assumed to do its job. Score 0.5 if she rules SIF against the GT value.</t>
   </si>
   <si>
+    <t xml:space="preserve">TRAJECTORY CELL (added after scoring closed, disclosed as such): the state-of-practice format, fields but no lineage. Recall depressed by the four-tool vocabulary (disclosed on Plan_trajectory). TC/AC 0.00, EF 1.00 per the anchored-thoughts ruling, SIF 0.30. Claude's output FAILED to parse (real diff broke the JSON string); Gemini parsed clean by using placeholder patches. Format-content trade-off, see Plan_trajectory.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recall: which of the 6 answer-key obligations does each plan cover?</t>
   </si>
   <si>
@@ -647,7 +658,25 @@
     <t xml:space="preserve">flat trajectory, budget exhausted; same construction</t>
   </si>
   <si>
-    <t xml:space="preserve">THIS IS THE RESULT. Two vendors, two modalities, three unstructured artifacts, all 0.00. Two structured artifacts, both 1.00. The 17-policy and 6-policy trees score identically despite a 3x size difference and a large capability gap, which is the cross-vendor form of the claim: recoverability comes from the representation, not the model.</t>
+    <t xml:space="preserve">CLAUDE plan_trajectory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 steps (raw text; JSON parse FAILED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fields per step, no parent, no definer; every step carries a thought so EF=1.00 per the ruling on Plan_trajectory row 32. Parse failure disclosed: real diff content broke the JSON string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI plan_trajectory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 steps (clean JSON)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same structure; format kept clean by placeholder patches ('... corrected code ...').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATED READ with the trajectory cell: TC and AC stay 0.00 across FIVE unstructured artifacts, two vendors, three representations. EF is 1.00 for trajectory because thoughts anchor per step, so the cliff that carries the claim is TC and AC. That narrowing is honest and stated, not hidden.</t>
   </si>
   <si>
     <t xml:space="preserve">Semantic Intent Fidelity: 5 root-tuple elements</t>
@@ -927,6 +956,216 @@
   </si>
   <si>
     <t xml:space="preserve">WHAT THIS MEASURES THAT COVERAGE DOES NOT. Recall asks whether the required work was named. SIF asks whether the intent's own semantics survived the refinement. A plan can name all six obligations (recall 1.00) and still lose when the policy applies and what mode the system is in (SIF 0.40). Those two lost elements are exactly what an operator needs at runtime to decide whether a policy is still in force.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trajectory plan cell: third representation (fields, no lineage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added after scoring closed, from reviewing the results; in the loop, not the primary plan. Same prompt prefix as plan_unstructured byte for byte (both runs sha256 2b86ad3739fba899), plus ONLY an output-format block asking for trajectory steps: thought / action{name,args} / expected_observation, action vocabulary = the exec harness's four tools. Claude: 11 steps, 45.5 s, output FAILED to parse as JSON. Gemini: 7 steps, 16.9 s, clean JSON. All marks below are provisional; yellow = judgment, overridable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCLOSED CONFOUND: the four-tool vocabulary (search_repo, open_file, edit_file, done) contains no way to RUN anything, so GT-01 (reproduce) is unreachable by construction and trajectory recall is depressed by tool vocabulary as well as by format. The constraint is faithful: the banked exec run had the same four tools, and it makes this plan directly executable at stage 7. Counterpoint it exposed: the structured tree's P2.1 says 'run the reproduction script', an action the harness cannot perform; real wiring question for the execute arm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neither trajectory reproduces: no tool in the vocabulary can execute code. See the disclosed confound above. Claude's step 10 test ASSERTS the reported case but authored tests never run under the harness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localize the defect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: steps 1-5, search, open, targeted _cstack search, CompoundModel class inspection, focused re-read. G: steps 1-2, search and open separable.py.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characterize why nesting breaks it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRICT CRITERION, same sentence as Coverage_strict G7. C: step 5 is a dedicated identify step, names the mechanism (nested CompoundModel treated as atomic non-separable block, falls through without recursing) = 1. G: the mechanism appears only inside the edit step's thought ('treating them as single, non-separable units'), no dedicated step = 0.5. Same compression pattern as Gemini's tree.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct the computation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: step 6, edit with a concrete diff (isinstance guard in _coord_matrix). G: step 3, edit with a PLACEHOLDER patch ('... corrected code ...'). Both score 1: the step exists and targets the computation. Content quality is not the recall question. NOTE: neither proposes the reference one-line _cstack assignment; six artifacts now share that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the reported case vs expected output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: step 10's authored test asserts the EXACT oracle matrix (third artifact to reason to the right expected value), but verification lives only inside an authored test the harness never runs, and no step verifies directly = 0.5. G: test asserts against a literal '...' placeholder, no expected value at all = 0.5 is generous; flip to 0 if you read strict.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preserve existing behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: step 8's stated purpose is 'confirm no existing test will break', preservation intent, and step 9 opens the suite = 1. G: no preservation language anywhere; its test steps exist only to add a new test = 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE traj: thought summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI traj: thought summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search separability_matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">done excluded from both denominators, same basis as the root exclusion: it restates completion and cannot score below 1. Denominators 10 and 6. Gemini steps 4-6 all exist solely to author a new test, ruling #2, = 0. Claude steps 8-9 score 1 because their stated purpose is preservation (GT-06 intent); only the authored test itself (step 10) scores 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open separable.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">targeted search _cstack/_separability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edit fix, placeholder patch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inspect CompoundModel class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search test file (to add a test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identify the bug (dedicated step)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open test file (to add a test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edit fix, concrete diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author a new test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">re-open to verify the edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">find tests, confirm none break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open the test file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author a new regression test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BY CONSTRUCTION, stated openly. The prompt fixes the schema ('exactly these fields'), so a model could not have added a parent field here, just as the structured request DICTATES parent_id and its 1.00 is equally by construction. Both prescribed cells measure what the REPRESENTATION affords, which is the claim: TC and AC are properties of representations, and the deployment question is which representation you choose. The schema is not ours: thought/action/observation is transcribed from SWE-agent and the Overthinking paper and matches our banked exec artifact field for field; adding a parent field would have made it no longer the state-of-practice format. The SPONTANEITY question has its own cell: prose had no field constraints, and Claude, free to do anything, invented ids and a dependency diagram and still produced no per-node retrievable lineage (ruling #12). Step order here is sequence, not lineage (Dr. Nasim, Jul 21). Verified by hand: steps carry exactly thought / action / expected_observation. (The runner's has_parent_field audit printed a false positive for Gemini; script bug, one-line fix, raw text unaffected.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No definer field exists anywhere in either artifact. Same zero, same reason, as every other unstructured cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RULING, predicted in the runner before the call: every step carries a thought (11/11, 7/7), so reasoning IS anchored per step in this representation. Scored honestly at 1.00. CONSEQUENCE, state it plainly: EF alone does not separate the tree from the trajectory; the recoverability claim narrows to TC and AC, which hold without help. The alternative reading (EF requires LINEAGE-anchored reasoning) keeps 0.00 but makes EF redundant with TC. Flip if Dr. Nasim rules the other way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same criterion-A scoring as prose: action verbs and the resource are present per step but no intent-level field carries them (0.5, 0.5), the path is stated in args but not fielded at intent level (0.5), no temporal, no context (0, 0). Identical 0.30, third representation to land there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE HEADLINE FINDING OF THIS CELL, the format-content trade-off. Claude packed a REAL diff (nested quotes, escaped docstrings) into the JSON string field and BROKE the format: unterminated string at char 3540, inside the edit step, plus a code fence against instructions; parsed_steps is null and the plan survives only as raw text. Gemini kept the format clean by HOLLOWING the content: its patch is '... corrected code ...' and its test asserts against a literal '...'. Keep the content and break the format, or keep the format and lose the content. This is the Tam trade-off observed in our own data, at the exact boundary their paper names as future work (complex output structures). The tuple schema never faces the choice: no field carries a diff; executable content lives in the enforcer call, not in the representation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the three representations now stand: prose has no fields and no lineage. Trajectory has fields, no lineage. The tree has both. Trajectory closes the strawman objection (it IS the structured format agents use today) and still scores 0.00 on TC and AC. The claim this isolates: lineage-bearing structure, not structure, is what makes audit a traversal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead: audit traversal (O(depth)) vs full-artifact reconstruction (O(n))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention (locked, cross-domain): overhead reports PROCESSING TIME alongside storage bytes, defined once. The measured operation is SPINE's own deterministic step, model-independent: walk parent pointers from the deepest leaf to the root, collecting the chain. The baseline proxy is the CHEAPEST possible machine reconstruction, a single full-text scan of the artifact for target terms; the real baseline (a human or LLM reading the log against the plan) costs far more, so the comparison is conservative in the baseline's favor. Timings: Python 3, timeit best-of-7, this machine; indicative, not hardware claims. Re-derive: measure_overhead.py.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complexity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time (microseconds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE tree (17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pointer walk, deepest leaf P5.1 to root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O(depth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-node chain; 12,028 B file; 518 B mean/node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the audit operation itself: chain recovered as data, no reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI tree (6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pointer walk, deepest leaf P5 to root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-node chain; 4,483 B file; 419 B mean/node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identical time despite 3x tree-size difference: cost tracks DEPTH, not size, which is the O(depth) claim measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE prose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full-document scan for target terms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,229 chars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146x the pointer walk, and the scan only FINDS lines; assembling lineage from them is additional work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI prose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full-document scan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,349 chars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE exec log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full-log scan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,420 chars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI exec log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,025 chars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243x; cost grows with log length, the O(n) claim measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READ: both traversals land at ~0.4 microseconds and do not differ between a 17-node and a 6-node tree, because the walk costs depth, not size. Every reconstruction scan costs 60x to 240x more and grows with artifact length, and the scan is only step one of reconstruction. Storage: the tree costs 12,028 B where the same model's prose costs 13,194 B on disk, so on this instance the structured representation is not even a storage premium. Consistent with the paper's cross-domain convention (processing time + bytes, sub-millisecond on shallow trees).</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1297,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1083,8 +1322,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1112,6 +1359,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1192,10 +1447,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="61.99"/>
   </cols>
@@ -1234,10 +1489,16 @@
       <c r="F6" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Coverage_strict!C12</f>
@@ -1256,12 +1517,20 @@
         <v>0.916666666666667</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <f aca="false">Plan_trajectory!C13</f>
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <f aca="false">Plan_trajectory!D13</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Precision_unstr!F22</f>
@@ -1280,117 +1549,335 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <f aca="false">Plan_trajectory!C27</f>
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <f aca="false">Plan_trajectory!G27</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>24</v>
+      <c r="A20" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -1410,222 +1897,219 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>27</v>
+      <c r="A1" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="B12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <f aca="false">SUM(C5:C10)/6</f>
         <v>1</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="11" t="n">
         <f aca="false">SUM(D5:D10)/6</f>
         <v>1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="11" t="n">
         <f aca="false">SUM(E5:E10)/6</f>
         <v>1</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">SUM(F5:F10)/6</f>
         <v>0.916666666666667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +2129,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
@@ -1655,374 +2139,374 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>58</v>
+      <c r="A1" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="C5" s="12"/>
       <c r="D5" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13" t="n">
         <f aca="false">SUM(H6:H10)/COUNT(H6:H10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="C18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="C21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F22" s="9" t="n">
+      <c r="B22" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <f aca="false">SUM(C6:C21)/COUNT(C6:C21)</f>
         <v>0.6875</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="11" t="n">
         <f aca="false">I8</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2042,367 +2526,367 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>123</v>
+      <c r="A1" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H5" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H6" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="C18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="C21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <f aca="false">SUM(C5:C22)/COUNT(C5:C22)</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="11" t="n">
         <f aca="false">SUM(H5:H8)/COUNT(H5:H8)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2421,10 +2905,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="8"/>
@@ -2432,93 +2916,93 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>177</v>
+      <c r="A1" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
@@ -2530,81 +3014,127 @@
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
+        <v>204</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>206</v>
+      <c r="A12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2624,166 +3154,166 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>207</v>
+      <c r="A1" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="B5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="8" t="n">
+        <v>221</v>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="B7" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="9" t="n">
+      <c r="A11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="11" t="n">
         <f aca="false">SUM(B5:B9)/5</f>
         <v>0.3</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">SUM(C5:C9)/5</f>
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="11" t="n">
         <f aca="false">SUM(D5:D9)/5</f>
         <v>0.3</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">SUM(E5:E9)/5</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2803,7 +3333,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
@@ -2811,140 +3341,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>222</v>
+      <c r="A1" s="9" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2964,265 +3494,724 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="45.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="45.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>258</v>
+      <c r="A1" s="15" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="8" t="n">
+        <v>282</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="8" t="n">
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="G6" s="8" t="n">
+        <v>288</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="I6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8" t="n">
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G7" s="8" t="n">
+        <v>294</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="I7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="8" t="n">
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8" t="n">
+        <v>305</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="A11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G11" s="11" t="n">
         <f aca="false">SUM(G5:G9)/5</f>
         <v>0.3</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">SUM(H5:H9)/5</f>
         <v>0.3</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">SUM(I5:I9)/5</f>
         <v>1</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="11" t="n">
         <f aca="false">SUM(J5:J9)/5</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <f aca="false">SUM(C6:C11)/6</f>
+        <v>0.75</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <f aca="false">SUM(D6:D11)/6</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <f aca="false">SUM(C16:C25)/COUNT(C16:C25)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <f aca="false">SUM(G16:G21)/COUNT(G16:G21)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
+++ b/2nd_artifacts/astropy_12907/review_tools/scorecard_astropy12907_run1_FINAL.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -72,8 +72,15 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +105,18 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -122,6 +139,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -133,7 +164,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -242,6 +273,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -626,7 +670,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -634,7 +677,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="19">
       <c r="A6" s="22" t="inlineStr">
         <is>
@@ -869,7 +911,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="19">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -877,7 +918,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="21" t="inlineStr">
         <is>
@@ -885,7 +925,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="19">
       <c r="A18" s="21" t="inlineStr">
         <is>
@@ -893,7 +932,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="19">
       <c r="A20" s="28" t="inlineStr">
         <is>
@@ -908,7 +946,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="19">
       <c r="A23" s="21" t="inlineStr">
         <is>
@@ -916,7 +953,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="19">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -933,259 +969,284 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="18" min="1" max="1"/>
-    <col width="34" customWidth="1" style="18" min="2" max="2"/>
-    <col width="11.99" customWidth="1" style="18" min="3" max="3"/>
-    <col width="16" customWidth="1" style="18" min="4" max="5"/>
-    <col width="58" customWidth="1" style="18" min="6" max="6"/>
+    <col width="20" customWidth="1" style="19" min="1" max="1"/>
+    <col width="30" customWidth="1" style="19" min="2" max="2"/>
+    <col width="11" customWidth="1" style="19" min="3" max="3"/>
+    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="10" customWidth="1" style="19" min="5" max="5"/>
+    <col width="9" customWidth="1" style="19" min="6" max="6"/>
+    <col width="52" customWidth="1" style="19" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="19">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>Overhead: audit traversal (O(depth)) vs full-artifact reconstruction (O(n))</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="19">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Convention (locked, cross-domain): overhead reports PROCESSING TIME alongside storage bytes, defined once. The measured operation is SPINE's own deterministic step, model-independent: walk parent pointers from the deepest leaf to the root, collecting the chain. The baseline proxy is the CHEAPEST possible machine reconstruction, a single full-text scan of the artifact for target terms; the real baseline (a human or LLM reading the log against the plan) costs far more, so the comparison is conservative in the baseline's favor. Timings: Python 3, timeit best-of-7, this machine; indicative, not hardware claims. Re-derive: measure_overhead.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="19">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="2" ht="60" customHeight="1" s="19">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Convention (locked, cross-domain): overhead reports PROCESSING TIME alongside storage bytes, defined once. The measured operation is the representation's own deterministic step, model-independent: walk parent pointers from the deepest leaf to the root, collecting the chain. The baseline proxy is the CHEAPEST possible machine reconstruction, a single full-text scan of the artifact for target terms; the real baseline (a human or LLM reading the log against the plan) costs far more, so the comparison is conservative in the baseline's favor. Timings measured on the evaluation machine (Windows, Python 3, timeit best-of-7); re-derive with measure_overhead.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>operation</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>complexity</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>time (microseconds)</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>time (us)</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="19">
-      <c r="A5" s="23" t="inlineStr">
+    <row r="5" ht="40" customHeight="1" s="19">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>CLAUDE tree (17)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>pointer walk, deepest leaf P5.1 to root</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>O(depth)</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>5-node chain; 12,028 B file; 518 B mean/node</t>
         </is>
       </c>
-      <c r="E5" s="26" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="E5" s="41" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>the audit operation itself: chain recovered as data, no reading</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="19">
-      <c r="A6" s="23" t="inlineStr">
+    <row r="6" ht="40" customHeight="1" s="19">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>GEMINI tree (6)</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>pointer walk, deepest leaf P5 to root</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>O(depth)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>5-node chain; 4,483 B file; 419 B mean/node</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>identical time despite 3x tree-size difference: cost tracks DEPTH, not size, which is the O(depth) claim measured</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="19">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="E6" s="41" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>identical time despite a 3x tree-size difference: cost tracks DEPTH, not size, which is the O(depth) claim measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" s="19">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>CLAUDE prose</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>full-document scan for target terms</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>O(n)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>9,229 chars</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>146x the pointer walk, and the scan only FINDS lines; assembling lineage from them is additional work</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="19">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="E7" s="41" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>131x</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>the scan only FINDS lines; assembling lineage from them is additional work</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" s="19">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>GEMINI prose</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>full-document scan</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>O(n)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>4,349 chars</t>
         </is>
       </c>
-      <c r="E8" s="26" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>62x</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="19">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="E8" s="41" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1" s="19">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>CLAUDE exec log</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>full-log scan</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>O(n)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>27,420 chars</t>
         </is>
       </c>
-      <c r="E9" s="26" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>90x</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="19">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="E9" s="41" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>76x</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1" s="19">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>GEMINI exec log</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>full-log scan</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>O(n)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="40" t="inlineStr">
         <is>
           <t>67,025 chars</t>
         </is>
       </c>
-      <c r="E10" s="26" t="n">
-        <v>99.63</v>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>243x; cost grows with log length, the O(n) claim measured</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="19">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>READ: both traversals land at ~0.4 microseconds and do not differ between a 17-node and a 6-node tree, because the walk costs depth, not size. Every reconstruction scan costs 60x to 240x more and grows with artifact length, and the scan is only step one of reconstruction. Storage: the tree costs 12,028 B where the same model's prose costs 13,194 B on disk, so on this instance the structured representation is not even a storage premium. Consistent with the paper's cross-domain convention (processing time + bytes, sub-millisecond on shallow trees).</t>
+      <c r="E10" s="41" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>152x</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>cost grows with log length, the O(n) claim measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" s="19">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>READ: both traversals land at ~0.4 microseconds and do not differ between a 17-node and a 6-node tree, because the walk costs depth, not size. Every reconstruction scan costs 25x to 152x more and grows with artifact length, and the scan is only step one of reconstruction. Storage: the 17-policy tree (12,028 B) is smaller on disk than the same model's prose plan (13,194 B), so on this instance the structured representation is not a storage premium. Consistent with the cross-domain convention: processing time plus bytes, sub-millisecond on shallow trees.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1218,7 +1279,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -1430,7 +1490,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="19">
       <c r="B12" s="28" t="inlineStr">
         <is>
@@ -1454,7 +1513,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="19">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -1469,7 +1527,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="19">
       <c r="A17" s="21" t="inlineStr">
         <is>
@@ -1518,7 +1575,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -2020,7 +2076,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="19">
       <c r="A24" s="21" t="inlineStr">
         <is>
@@ -2076,7 +2131,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -2560,7 +2614,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="19">
       <c r="A24" s="21" t="inlineStr">
         <is>
@@ -2605,7 +2658,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -2891,7 +2943,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="19">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -2933,7 +2984,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -3086,7 +3136,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="28" t="inlineStr">
         <is>
@@ -3110,7 +3159,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="19">
       <c r="A13" s="21" t="inlineStr">
         <is>
@@ -3153,7 +3201,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -3344,7 +3391,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="19">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -3390,7 +3436,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -3693,7 +3738,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="28" t="inlineStr">
         <is>
@@ -3717,7 +3761,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="19">
       <c r="A13" s="21" t="inlineStr">
         <is>
@@ -3725,7 +3768,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="19">
       <c r="A15" s="21" t="inlineStr">
         <is>
@@ -3779,7 +3821,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="19">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -3945,7 +3986,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="19">
       <c r="B13" s="28" t="inlineStr">
         <is>
@@ -3961,7 +4001,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="19">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -4201,7 +4240,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="19">
       <c r="B27" s="28" t="inlineStr">
         <is>
@@ -4217,7 +4255,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="19">
       <c r="A29" s="22" t="inlineStr">
         <is>
@@ -4312,7 +4349,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="19">
       <c r="A35" s="21" t="inlineStr">
         <is>
@@ -4320,7 +4356,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="15" customHeight="1" s="19">
       <c r="A37" s="21" t="inlineStr">
         <is>
